--- a/config/Config/Data/__tables__.xlsx
+++ b/config/Config/Data/__tables__.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="87">
   <si>
     <t>##var</t>
   </si>
@@ -260,6 +260,18 @@
   </si>
   <si>
     <t>龙南大事件与97届兄弟纪年</t>
+  </si>
+  <si>
+    <t>TbRoleVoice</t>
+  </si>
+  <si>
+    <t>RoleVoice</t>
+  </si>
+  <si>
+    <t>RoleVoice@语音.xlsx</t>
+  </si>
+  <si>
+    <t>人声文案</t>
   </si>
 </sst>
 </file>
@@ -636,7 +648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1092,6 +1104,32 @@
         <v>82</v>
       </c>
     </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
+        <v>85</v>
+      </c>
+      <c r="F16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" t="s">
+        <v>28</v>
+      </c>
+      <c r="I16" t="s">
+        <v>86</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
